--- a/artfynd/A 938-2024 artfynd.xlsx
+++ b/artfynd/A 938-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115381868</v>
+        <v>115825881</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589095</v>
+        <v>589205</v>
       </c>
       <c r="R2" t="n">
-        <v>6425799</v>
+        <v>6425914</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ganska många fruktkroppar på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,12 +788,7 @@
         <v>115387607</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115826365</v>
+        <v>115381868</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589053</v>
+        <v>589095</v>
       </c>
       <c r="R4" t="n">
-        <v>6425830</v>
+        <v>6425799</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,12 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,46 +999,40 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115826393</v>
+        <v>115825735</v>
       </c>
       <c r="B5" t="n">
-        <v>5479</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1058,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589054</v>
+        <v>589118</v>
       </c>
       <c r="R5" t="n">
-        <v>6425827</v>
+        <v>6425788</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,12 +1107,7 @@
         <v>115825808</v>
       </c>
       <c r="B6" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,46 +1209,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115825881</v>
+        <v>115826365</v>
       </c>
       <c r="B7" t="n">
-        <v>89418</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>889</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1278,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589205</v>
+        <v>589053</v>
       </c>
       <c r="R7" t="n">
-        <v>6425914</v>
+        <v>6425830</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,18 +1290,12 @@
           <t>2024-04-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ganska många fruktkroppar på tall</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,6 +1311,222 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115826393</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 938, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589054</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6425827</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115825762</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 938, Hjulby, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589189</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6425868</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
